--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/ValueSet-tddui-serafin-valueset.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/ValueSet-tddui-serafin-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T14:23:39+00:00</t>
+    <t>2026-01-28T15:00:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
